--- a/NECP Scenario/Results/Regional Results/EL64_Capacity.xlsx
+++ b/NECP Scenario/Results/Regional Results/EL64_Capacity.xlsx
@@ -507,25 +507,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.176540013516382E-11</v>
+        <v>1.737116930146701E-11</v>
       </c>
       <c r="C2">
-        <v>6.160912225426086E-12</v>
+        <v>9.096367988519496E-12</v>
       </c>
       <c r="D2">
-        <v>9.052358598716096E-12</v>
+        <v>1.336547708925743E-11</v>
       </c>
       <c r="E2">
-        <v>1.330098892083755E-11</v>
+        <v>1.96384081680031E-11</v>
       </c>
       <c r="F2">
-        <v>1.954359042826088E-11</v>
+        <v>2.885535409238721E-11</v>
       </c>
       <c r="G2">
-        <v>2.87158862024704E-11</v>
+        <v>4.239789015332537E-11</v>
       </c>
       <c r="H2">
-        <v>1.740402298358392E-10</v>
+        <v>2.569638036150539E-10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,25 +533,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.45498808796626E-08</v>
+        <v>3.637616163705516E-08</v>
       </c>
       <c r="C3">
-        <v>2.461393719161141E-08</v>
+        <v>3.647278907293379E-08</v>
       </c>
       <c r="D3">
-        <v>5.51373618283229E-08</v>
+        <v>8.216699392537648E-08</v>
       </c>
       <c r="E3">
-        <v>9.92363912454145E-08</v>
+        <v>1.422517186962568E-07</v>
       </c>
       <c r="F3">
-        <v>2.334379123884153E-07</v>
+        <v>3.509540736333533E-07</v>
       </c>
       <c r="G3">
-        <v>5.909425697486739E-07</v>
+        <v>1.148330720632922E-06</v>
       </c>
       <c r="H3">
-        <v>5.759513673127154E-06</v>
+        <v>9.13707387313236E-06</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,22 +562,22 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.0290619069375113</v>
+        <v>0.0290681043119176</v>
       </c>
       <c r="D4">
-        <v>0.0290619069596027</v>
+        <v>0.0290681043498906</v>
       </c>
       <c r="E4">
-        <v>0.036162020927828</v>
+        <v>0.035841690625171</v>
       </c>
       <c r="F4">
-        <v>0.0403307088154062</v>
+        <v>0.0403078392151729</v>
       </c>
       <c r="G4">
-        <v>0.0435872170286672</v>
+        <v>0.0436749279578021</v>
       </c>
       <c r="H4">
-        <v>0.0477659863814982</v>
+        <v>0.0478238219070194</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -692,22 +692,22 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>1.45890683938827E-08</v>
+        <v>2.164158046804364E-08</v>
       </c>
       <c r="D9">
-        <v>1.640463370199631E-08</v>
+        <v>2.472148575631387E-08</v>
       </c>
       <c r="E9">
-        <v>1.661665269435355E-08</v>
+        <v>2.492425510614568E-08</v>
       </c>
       <c r="F9">
-        <v>1.664218965816135E-08</v>
+        <v>2.495926683274108E-08</v>
       </c>
       <c r="G9">
-        <v>1.669049152901913E-08</v>
+        <v>2.502724743269764E-08</v>
       </c>
       <c r="H9">
-        <v>8.763362083511842E-08</v>
+        <v>1.305885468591471E-07</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -793,25 +793,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3.984282764004172</v>
+        <v>3.984282764004715</v>
       </c>
       <c r="C13">
-        <v>3.984282764005897</v>
+        <v>3.98428276400726</v>
       </c>
       <c r="D13">
-        <v>3.984282764010008</v>
+        <v>3.984282764012976</v>
       </c>
       <c r="E13">
-        <v>3.984282764016374</v>
+        <v>3.984282764020901</v>
       </c>
       <c r="F13">
-        <v>3.98428276402972</v>
+        <v>3.984282764038116</v>
       </c>
       <c r="G13">
-        <v>3.984282764053606</v>
+        <v>3.984282764071951</v>
       </c>
       <c r="H13">
-        <v>3.984282764292543</v>
+        <v>3.984282764364641</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -923,25 +923,25 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>1.765791471004858E-08</v>
+        <v>2.612296616006666E-08</v>
       </c>
       <c r="C18">
-        <v>1.766816816394455E-08</v>
+        <v>2.613847893432703E-08</v>
       </c>
       <c r="D18">
-        <v>3.269010838717736E-08</v>
+        <v>4.902681837769995E-08</v>
       </c>
       <c r="E18">
-        <v>6.007110534184629E-08</v>
+        <v>8.874288616977682E-08</v>
       </c>
       <c r="F18">
-        <v>1.235482212072081E-07</v>
+        <v>1.851751692002649E-07</v>
       </c>
       <c r="G18">
-        <v>1.87485573437886E-07</v>
+        <v>3.133768796130859E-07</v>
       </c>
       <c r="H18">
-        <v>1.17121630334157E-06</v>
+        <v>1.761654576432857E-06</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1027,25 +1027,25 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>1.710992473872744E-08</v>
+        <v>2.542307732464912E-08</v>
       </c>
       <c r="C22">
-        <v>1.713689001391485E-08</v>
+        <v>2.546362179875864E-08</v>
       </c>
       <c r="D22">
-        <v>1.952857003545633E-08</v>
+        <v>2.899466918228318E-08</v>
       </c>
       <c r="E22">
-        <v>2.758050218723229E-08</v>
+        <v>4.083135197206717E-08</v>
       </c>
       <c r="F22">
-        <v>3.724355216741474E-08</v>
+        <v>5.503213000643559E-08</v>
       </c>
       <c r="G22">
-        <v>5.472016651747635E-08</v>
+        <v>8.615185500862371E-08</v>
       </c>
       <c r="H22">
-        <v>0.5455854681822117</v>
+        <v>0.740608592669774</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>6.073561683584068E-09</v>
+        <v>8.940077203815126E-09</v>
       </c>
       <c r="D24">
-        <v>2.385058774514811E-08</v>
+        <v>3.579366058057005E-08</v>
       </c>
       <c r="E24">
-        <v>1.183563095013219E-07</v>
+        <v>1.747557296415552E-07</v>
       </c>
       <c r="F24">
-        <v>3.461020300646812</v>
+        <v>3.377376255788286</v>
       </c>
       <c r="G24">
-        <v>6.489967708174729</v>
+        <v>6.911388874862228</v>
       </c>
       <c r="H24">
-        <v>8.90561529223366</v>
+        <v>8.973338808035589</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1160,22 +1160,22 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.3784381390681593</v>
+        <v>0.6145958386022935</v>
       </c>
       <c r="D27">
-        <v>3.497329804225275</v>
+        <v>3.497329804259726</v>
       </c>
       <c r="E27">
-        <v>3.497329804709707</v>
+        <v>3.497329804664509</v>
       </c>
       <c r="F27">
-        <v>3.497329804857281</v>
+        <v>3.497329804814588</v>
       </c>
       <c r="G27">
-        <v>3.497329804918468</v>
+        <v>3.497329804888858</v>
       </c>
       <c r="H27">
-        <v>3.497329804961792</v>
+        <v>3.497329804947765</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1212,22 +1212,22 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>7.558901276750592E-09</v>
+        <v>1.117367363562427E-08</v>
       </c>
       <c r="D29">
-        <v>2.251774576327948E-08</v>
+        <v>3.416677310529636E-08</v>
       </c>
       <c r="E29">
-        <v>4.885183348460056E-08</v>
+        <v>7.436802622702955E-08</v>
       </c>
       <c r="F29">
-        <v>1.098983783283377E-07</v>
+        <v>1.693713025205892E-07</v>
       </c>
       <c r="G29">
-        <v>3.010800035154049E-07</v>
+        <v>4.819458238145439E-07</v>
       </c>
       <c r="H29">
-        <v>0.4750819057397456</v>
+        <v>0.5830271565141123</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1264,22 +1264,22 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>1.125030569450518E-08</v>
+        <v>1.660250324907414E-08</v>
       </c>
       <c r="D31">
-        <v>1.174161723916714E-08</v>
+        <v>1.76194799663695E-08</v>
       </c>
       <c r="E31">
-        <v>2.34153851560694E-08</v>
+        <v>3.54931724928753E-08</v>
       </c>
       <c r="F31">
-        <v>4.221937612080552E-08</v>
+        <v>6.377357067416263E-08</v>
       </c>
       <c r="G31">
-        <v>5.41040212279465E-08</v>
+        <v>8.182446849597892E-08</v>
       </c>
       <c r="H31">
-        <v>3.014663828188014E-07</v>
+        <v>4.591245830823962E-07</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1316,22 +1316,22 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>3.038514220521225</v>
+        <v>3.264306225851209</v>
       </c>
       <c r="D33">
-        <v>3.038514220586869</v>
+        <v>3.264306225951961</v>
       </c>
       <c r="E33">
-        <v>4.480212012121664</v>
+        <v>5.094062099038092</v>
       </c>
       <c r="F33">
-        <v>4.480212012269868</v>
+        <v>5.094062099241228</v>
       </c>
       <c r="G33">
-        <v>4.480212012397307</v>
+        <v>5.094062099400191</v>
       </c>
       <c r="H33">
-        <v>4.480212013075625</v>
+        <v>5.094062100187007</v>
       </c>
     </row>
     <row r="34" spans="1:8">
